--- a/db/A7XLK-2603-MedicalService.xlsx
+++ b/db/A7XLK-2603-MedicalService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A350C14-F7FE-6245-A8E1-26259028740B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3023BF24-1AEA-B444-B501-681C6B88D8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="10840" windowWidth="27960" windowHeight="17060" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -131,10 +131,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NT$300/劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>羅氏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -143,10 +139,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NT$2,000 /盒, 共5劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.fda.gov.tw/tc/siteList.aspx?sid=11747</t>
   </si>
   <si>
@@ -215,6 +207,94 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=ikEK2EC_okc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>NT$300/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>劑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (實名制採購 NT$100/劑)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>NT$2,000 /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>共</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>劑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (實名制採購 NT$100/劑)</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -684,10 +764,10 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>24</v>
@@ -696,10 +776,10 @@
         <v>25</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>16</v>
@@ -725,10 +805,10 @@
         <v>0.98099999999999998</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>17</v>
@@ -742,10 +822,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>24</v>
@@ -757,10 +837,10 @@
         <v>0.91200000000000003</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>18</v>
@@ -774,13 +854,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -789,10 +869,10 @@
         <v>0.85</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>19</v>
@@ -806,10 +886,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>24</v>
@@ -821,10 +901,10 @@
         <v>0.94</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
@@ -838,10 +918,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>24</v>
@@ -850,7 +930,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>21</v>

--- a/db/A7XLK-2603-MedicalService.xlsx
+++ b/db/A7XLK-2603-MedicalService.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3023BF24-1AEA-B444-B501-681C6B88D8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1EFCB6-DFBF-2C4C-943B-E22EEB0A03FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
@@ -230,13 +230,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (實名制採購 NT$100/劑)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>NT$2,000 /</t>
+      <t xml:space="preserve"> (</t>
     </r>
     <r>
       <rPr>
@@ -246,7 +240,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>盒</t>
+      <t>實名制採購</t>
     </r>
     <r>
       <rPr>
@@ -255,7 +249,13 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> NT$500/盒 5劑/盒)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>NT$2,000 /</t>
     </r>
     <r>
       <rPr>
@@ -265,7 +265,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>共</t>
+      <t>盒</t>
     </r>
     <r>
       <rPr>
@@ -274,7 +274,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>5</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -284,7 +284,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>劑</t>
+      <t>共</t>
     </r>
     <r>
       <rPr>
@@ -293,7 +293,64 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (實名制採購 NT$100/劑)</t>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>劑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>實名制採購</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NT$500/盒 5劑/盒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>劑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -721,7 +778,7 @@
     <col min="4" max="4" width="16.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="3"/>
     <col min="6" max="6" width="15.5" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="26.83203125" style="4" customWidth="1"/>
     <col min="9" max="9" width="49.1640625" style="2" customWidth="1"/>
     <col min="10" max="16384" width="10.83203125" style="2"/>

--- a/db/A7XLK-2603-MedicalService.xlsx
+++ b/db/A7XLK-2603-MedicalService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1EFCB6-DFBF-2C4C-943B-E22EEB0A03FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E8D0AC-6B8B-3148-921D-83053B7A0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="1220" yWindow="2700" windowWidth="27920" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -352,6 +352,14 @@
       </rPr>
       <t>)</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>95.60 % for NP swab; 90.20% for a nasal swab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAD$9.5/劑</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -832,6 +840,12 @@
       <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="H2" s="6" t="s">
         <v>45</v>
       </c>

--- a/db/A7XLK-2603-MedicalService.xlsx
+++ b/db/A7XLK-2603-MedicalService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E8D0AC-6B8B-3148-921D-83053B7A0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10BC96A-E5ED-494D-90F8-2D6AFC94BF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="2700" windowWidth="27920" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="1860" yWindow="720" windowWidth="31120" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -187,10 +187,6 @@
   </si>
   <si>
     <t>新冠病毒 Omicron 快速測試套裝</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NT$500</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -360,6 +356,86 @@
   </si>
   <si>
     <t>CAD$9.5/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗原試劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>核酸檢驗試劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-263-Antigen/XLK-2601-NAAT-01.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-263-Antigen/XLK-2601-NAAT-02.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盧西拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用確可易新型冠狀病毒核酸檢測試劑 Lucira CHECK-IT COVID-19 Test Kit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NT$1,800/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NT$500/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.deltaasia.com.tw/proimage/control_page/%E7%9B%A7%E8%A5%BF%E6%8B%89%E7%A2%BA%E5%8F%AF%E6%98%93%E6%96%B0%E5%9E%8B%E5%86%A0%E7%8B%80%E7%97%85%E6%AF%92%E6%A0%B8%E9%85%B8%E6%AA%A2%E6%B8%AC%E8%A9%A6%E5%8A%91%E5%8E%9F%E7%90%86%E5%8F%8A%E8%87%A8%E5%BA%8A%E6%B8%AC%E8%A9%A6%E4%B8%AD%E6%96%87%E8%AA%AA%E6%98%8E%E6%9B%B8.pdf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>萊析樂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NT$3,000/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.fda.gov.tw/TC/siteList.aspx?sid=11746</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>家用新冠病毒核酸檢測組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Lucira CHECK-IT COVID-19 Test Kit</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -370,7 +446,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -408,6 +484,13 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -434,7 +517,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -460,6 +543,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,22 +863,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="3"/>
-    <col min="6" max="6" width="15.5" style="5" customWidth="1"/>
-    <col min="7" max="7" width="38.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="49.1640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="2"/>
+    <col min="2" max="3" width="14.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="3"/>
+    <col min="7" max="7" width="15.5" style="5" customWidth="1"/>
+    <col min="8" max="8" width="38.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="49.1640625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17">
+    <row r="1" spans="1:11" ht="17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,63 +886,69 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32">
+    <row r="2" spans="1:11" ht="32">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="J2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="32">
+    <row r="3" spans="1:11" ht="32">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -864,31 +956,34 @@
         <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="5">
+      <c r="G3" s="5">
         <v>0.98099999999999998</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="34">
+    <row r="4" spans="1:11" ht="34">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -896,63 +991,69 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="5">
+      <c r="G4" s="5">
         <v>0.91200000000000003</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="32">
+    <row r="5" spans="1:11" ht="32">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="5">
+      <c r="G5" s="5">
         <v>0.85</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="32">
+    <row r="6" spans="1:11" ht="32">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -960,31 +1061,34 @@
         <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
         <v>0.94</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17">
+    <row r="7" spans="1:11" ht="17">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -992,31 +1096,105 @@
         <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="H7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="306">
+      <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="32">
+      <c r="A9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{BBC4BAAE-7C18-0A4B-807E-EC969492AB14}"/>
-    <hyperlink ref="H5" r:id="rId2" xr:uid="{B9C8A035-A319-B943-807C-9C0C8C2CBFF7}"/>
-    <hyperlink ref="H6" r:id="rId3" xr:uid="{3DB542F2-1BB2-1942-B455-EE1ACB012F87}"/>
-    <hyperlink ref="H2" r:id="rId4" xr:uid="{F6C424E5-1E2B-7141-A845-6A2392948233}"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{BBC4BAAE-7C18-0A4B-807E-EC969492AB14}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{B9C8A035-A319-B943-807C-9C0C8C2CBFF7}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{3DB542F2-1BB2-1942-B455-EE1ACB012F87}"/>
+    <hyperlink ref="I2" r:id="rId4" xr:uid="{F6C424E5-1E2B-7141-A845-6A2392948233}"/>
+    <hyperlink ref="I9" r:id="rId5" xr:uid="{FA66358F-57DD-EC4D-B732-55B1AA2A8CEB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2603-MedicalService.xlsx
+++ b/db/A7XLK-2603-MedicalService.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10BC96A-E5ED-494D-90F8-2D6AFC94BF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637F34D8-362D-8B40-88AE-02CB43F193D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="720" windowWidth="31120" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -207,7 +207,7 @@
   </si>
   <si>
     <r>
-      <t>NT$300/</t>
+      <t>NT$2,000 /</t>
     </r>
     <r>
       <rPr>
@@ -217,7 +217,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>劑</t>
+      <t>盒</t>
     </r>
     <r>
       <rPr>
@@ -226,7 +226,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -236,7 +236,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>實名制採購</t>
+      <t>共</t>
     </r>
     <r>
       <rPr>
@@ -245,13 +245,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> NT$500/盒 5劑/盒)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>NT$2,000 /</t>
+      <t>5</t>
     </r>
     <r>
       <rPr>
@@ -261,7 +255,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>盒</t>
+      <t>劑</t>
     </r>
     <r>
       <rPr>
@@ -270,7 +264,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> (</t>
     </r>
     <r>
       <rPr>
@@ -280,7 +274,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>共</t>
+      <t>實名制採購</t>
     </r>
     <r>
       <rPr>
@@ -289,7 +283,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>5</t>
+      <t xml:space="preserve"> NT$500/盒 5劑/盒</t>
     </r>
     <r>
       <rPr>
@@ -308,8 +302,77 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>95.60 % for NP swab; 90.20% for a nasal swab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAD$9.5/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗原試劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>核酸檢驗試劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-263-Antigen/XLK-2601-NAAT-01.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-263-Antigen/XLK-2601-NAAT-02.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盧西拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用確可易新型冠狀病毒核酸檢測試劑 Lucira CHECK-IT COVID-19 Test Kit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NT$1,800/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NT$500/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.deltaasia.com.tw/proimage/control_page/%E7%9B%A7%E8%A5%BF%E6%8B%89%E7%A2%BA%E5%8F%AF%E6%98%93%E6%96%B0%E5%9E%8B%E5%86%A0%E7%8B%80%E7%97%85%E6%AF%92%E6%A0%B8%E9%85%B8%E6%AA%A2%E6%B8%AC%E8%A9%A6%E5%8A%91%E5%8E%9F%E7%90%86%E5%8F%8A%E8%87%A8%E5%BA%8A%E6%B8%AC%E8%A9%A6%E4%B8%AD%E6%96%87%E8%AA%AA%E6%98%8E%E6%9B%B8.pdf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>萊析樂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NT$3,000/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.fda.gov.tw/TC/siteList.aspx?sid=11746</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -318,7 +381,7 @@
         <family val="1"/>
         <charset val="136"/>
       </rPr>
-      <t>實名制採購</t>
+      <t>家用新冠病毒核酸檢測組</t>
     </r>
     <r>
       <rPr>
@@ -327,7 +390,13 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> NT$500/盒 5劑/盒</t>
+      <t xml:space="preserve"> Lucira CHECK-IT COVID-19 Test Kit</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>NT$300/</t>
     </r>
     <r>
       <rPr>
@@ -346,95 +415,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>95.60 % for NP swab; 90.20% for a nasal swab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAD$9.5/劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>008</t>
-  </si>
-  <si>
-    <t>Type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>抗原試劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>核酸檢驗試劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-263-Antigen/XLK-2601-NAAT-01.jpeg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-263-Antigen/XLK-2601-NAAT-02.jpeg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>盧西拉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>家用確可易新型冠狀病毒核酸檢測試劑 Lucira CHECK-IT COVID-19 Test Kit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NT$1,800/劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NT$500/劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.deltaasia.com.tw/proimage/control_page/%E7%9B%A7%E8%A5%BF%E6%8B%89%E7%A2%BA%E5%8F%AF%E6%98%93%E6%96%B0%E5%9E%8B%E5%86%A0%E7%8B%80%E7%97%85%E6%AF%92%E6%A0%B8%E9%85%B8%E6%AA%A2%E6%B8%AC%E8%A9%A6%E5%8A%91%E5%8E%9F%E7%90%86%E5%8F%8A%E8%87%A8%E5%BA%8A%E6%B8%AC%E8%A9%A6%E4%B8%AD%E6%96%87%E8%AA%AA%E6%98%8E%E6%9B%B8.pdf</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>萊析樂</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NT$3,000/劑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.fda.gov.tw/TC/siteList.aspx?sid=11746</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="PMingLiU"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>家用新冠病毒核酸檢測組</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Lucira CHECK-IT COVID-19 Test Kit</t>
+      <t xml:space="preserve"> (由公務部門發放公費試劑)</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -886,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -921,7 +902,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>43</v>
@@ -933,10 +914,10 @@
         <v>25</v>
       </c>
       <c r="G2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>44</v>
@@ -956,7 +937,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>23</v>
@@ -971,7 +952,7 @@
         <v>0.98099999999999998</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>29</v>
@@ -991,7 +972,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>27</v>
@@ -1006,7 +987,7 @@
         <v>0.91200000000000003</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>28</v>
@@ -1026,7 +1007,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>34</v>
@@ -1061,7 +1042,7 @@
         <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>36</v>
@@ -1096,7 +1077,7 @@
         <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>40</v>
@@ -1108,7 +1089,7 @@
         <v>25</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>21</v>
@@ -1119,16 +1100,16 @@
     </row>
     <row r="8" spans="1:11" ht="306">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>31</v>
@@ -1140,13 +1121,13 @@
         <v>0.9</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>16</v>
@@ -1154,16 +1135,16 @@
     </row>
     <row r="9" spans="1:11" ht="32">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>31</v>
@@ -1175,13 +1156,13 @@
         <v>0.9</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>16</v>

--- a/db/A7XLK-2603-MedicalService.xlsx
+++ b/db/A7XLK-2603-MedicalService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637F34D8-362D-8B40-88AE-02CB43F193D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E2D8A1-0571-5D42-8823-26628D5C9451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="1700" yWindow="1820" windowWidth="31640" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -417,6 +417,38 @@
       </rPr>
       <t xml:space="preserve"> (由公務部門發放公費試劑)</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>唾液快篩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用新型冠狀病毒唾液抗原快速檢驗套組</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>福吉美</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-263-Antigen/XLK-2601-Antigen-71.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NT$175/劑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ct值小於23、24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.fda.gov.tw/TC/siteList.aspx?sid=12124</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -844,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B99F67C-5614-8346-BE95-8F889F8DAB55}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
@@ -896,34 +928,34 @@
     </row>
     <row r="2" spans="1:11" ht="32">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>16</v>
@@ -931,16 +963,16 @@
     </row>
     <row r="3" spans="1:11" ht="32">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>24</v>
@@ -948,34 +980,34 @@
       <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="5">
-        <v>0.98099999999999998</v>
+      <c r="G3" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="34">
+    <row r="4" spans="1:11" ht="32">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>24</v>
@@ -984,51 +1016,51 @@
         <v>25</v>
       </c>
       <c r="G4" s="5">
-        <v>0.91200000000000003</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>28</v>
+        <v>64</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="32">
+    <row r="5" spans="1:11" ht="34">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>31</v>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="5">
-        <v>0.85</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>33</v>
+        <v>45</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>16</v>
@@ -1036,51 +1068,51 @@
     </row>
     <row r="6" spans="1:11" ht="32">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>24</v>
+      <c r="D6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="5">
-        <v>0.94</v>
+        <v>0.85</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="17">
+    <row r="7" spans="1:11" ht="32">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>24</v>
@@ -1088,63 +1120,63 @@
       <c r="F7" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="G7" s="5">
+        <v>0.94</v>
+      </c>
       <c r="H7" s="1" t="s">
-        <v>58</v>
+        <v>37</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="306">
+    <row r="8" spans="1:11" ht="17">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="5">
-        <v>0.9</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="32">
+    <row r="9" spans="1:11" ht="306">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>63</v>
+      <c r="D9" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>31</v>
@@ -1156,26 +1188,62 @@
         <v>0.9</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="32">
+      <c r="A10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{BBC4BAAE-7C18-0A4B-807E-EC969492AB14}"/>
-    <hyperlink ref="I5" r:id="rId2" xr:uid="{B9C8A035-A319-B943-807C-9C0C8C2CBFF7}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{3DB542F2-1BB2-1942-B455-EE1ACB012F87}"/>
-    <hyperlink ref="I2" r:id="rId4" xr:uid="{F6C424E5-1E2B-7141-A845-6A2392948233}"/>
-    <hyperlink ref="I9" r:id="rId5" xr:uid="{FA66358F-57DD-EC4D-B732-55B1AA2A8CEB}"/>
+    <hyperlink ref="I4" r:id="rId1" xr:uid="{BBC4BAAE-7C18-0A4B-807E-EC969492AB14}"/>
+    <hyperlink ref="I6" r:id="rId2" xr:uid="{B9C8A035-A319-B943-807C-9C0C8C2CBFF7}"/>
+    <hyperlink ref="I7" r:id="rId3" xr:uid="{3DB542F2-1BB2-1942-B455-EE1ACB012F87}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{F6C424E5-1E2B-7141-A845-6A2392948233}"/>
+    <hyperlink ref="I10" r:id="rId5" xr:uid="{FA66358F-57DD-EC4D-B732-55B1AA2A8CEB}"/>
+    <hyperlink ref="I2" r:id="rId6" xr:uid="{51F69F4D-9208-0F49-B280-785D171B5E3E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2603-MedicalService.xlsx
+++ b/db/A7XLK-2603-MedicalService.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E2D8A1-0571-5D42-8823-26628D5C9451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC44144-FE49-A344-9C0E-7BE2E652EB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="1820" windowWidth="31640" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
+    <workbookView xWindow="1220" yWindow="960" windowWidth="27940" windowHeight="17500" xr2:uid="{1D145BEA-DF54-D44B-94A9-174F6DE5B3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -449,6 +449,10 @@
   </si>
   <si>
     <t>https://www.fda.gov.tw/TC/siteList.aspx?sid=12124</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.fda.gov.tw/tc/siteList.aspx?sid=11964&amp;pn=2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1136,7 +1140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="17">
+    <row r="8" spans="1:11" ht="32">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -1157,6 +1161,9 @@
       </c>
       <c r="H8" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>21</v>
@@ -1244,6 +1251,7 @@
     <hyperlink ref="I3" r:id="rId4" xr:uid="{F6C424E5-1E2B-7141-A845-6A2392948233}"/>
     <hyperlink ref="I10" r:id="rId5" xr:uid="{FA66358F-57DD-EC4D-B732-55B1AA2A8CEB}"/>
     <hyperlink ref="I2" r:id="rId6" xr:uid="{51F69F4D-9208-0F49-B280-785D171B5E3E}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{B06DC006-76AF-8E44-BC05-328364B6D98B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
